--- a/gte/nodes/LPC/compressor_stage_3_blade_rotor_coordinates_foil.xlsx
+++ b/gte/nodes/LPC/compressor_stage_3_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0018719410415698968</v>
       </c>
       <c r="B2">
-        <v>0.0022409204999123775</v>
+        <v>0.0021771955569952033</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0037438820831397937</v>
       </c>
       <c r="B3">
-        <v>0.00356852027693836</v>
+        <v>0.003446053240406454</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0056158231247096912</v>
       </c>
       <c r="B4">
-        <v>0.00472562622939822</v>
+        <v>0.0045490595250657255</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0074877641662795874</v>
       </c>
       <c r="B5">
-        <v>0.0057548078898842286</v>
+        <v>0.0055284843154167493</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0093597052078494836</v>
       </c>
       <c r="B6">
-        <v>0.0066741004039206006</v>
+        <v>0.006402096945355284</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.011231646249419382</v>
       </c>
       <c r="B7">
-        <v>0.0074941796590923459</v>
+        <v>0.0071803450954374846</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.013103587290989278</v>
       </c>
       <c r="B8">
-        <v>0.0082217023621123531</v>
+        <v>0.0078696739445973784</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.014975528332559175</v>
       </c>
       <c r="B9">
-        <v>0.0088663607558297775</v>
+        <v>0.0084795978606172374</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.016847469374129072</v>
       </c>
       <c r="B10">
-        <v>0.0094384858140972028</v>
+        <v>0.00902028467613178</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.018719410415698967</v>
       </c>
       <c r="B11">
-        <v>0.00994792789864468</v>
+        <v>0.0095014468943372919</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.020591351457268866</v>
       </c>
       <c r="B12">
-        <v>0.010400219741482057</v>
+        <v>0.0099284909281122432</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.022463292498838765</v>
       </c>
       <c r="B13">
-        <v>0.010784104167860933</v>
+        <v>0.010290054158502308</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.024335233540408657</v>
       </c>
       <c r="B14">
-        <v>0.011093022093235185</v>
+        <v>0.010579481938516116</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.026207174581978555</v>
       </c>
       <c r="B15">
-        <v>0.011355996700626019</v>
+        <v>0.01082572054084688</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.028079115623548451</v>
       </c>
       <c r="B16">
-        <v>0.011599643418617432</v>
+        <v>0.011055316124700836</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.029951056665118349</v>
       </c>
       <c r="B17">
-        <v>0.011805364390477172</v>
+        <v>0.011249613475651695</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.031822997706688248</v>
       </c>
       <c r="B18">
-        <v>0.011949006973358857</v>
+        <v>0.011384411231847788</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.033694938748258144</v>
       </c>
       <c r="B19">
-        <v>0.012029412665275801</v>
+        <v>0.011458524815368413</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.035566879789828039</v>
       </c>
       <c r="B20">
-        <v>0.012051171499456231</v>
+        <v>0.011476523844275607</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.037438820831397934</v>
       </c>
       <c r="B21">
-        <v>0.012018873509128383</v>
+        <v>0.011442977936631413</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.03931076187296783</v>
       </c>
       <c r="B22">
-        <v>0.011936274871000173</v>
+        <v>0.011361629506332118</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.041182702914537732</v>
       </c>
       <c r="B23">
-        <v>0.011803796335698268</v>
+        <v>0.01123291215061099</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.043054643956107627</v>
       </c>
       <c r="B24">
-        <v>0.011621024797329016</v>
+        <v>0.011056432262535543</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.044926584997677529</v>
       </c>
       <c r="B25">
-        <v>0.01138754714999877</v>
+        <v>0.010831796235173294</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.046798526039247418</v>
       </c>
       <c r="B26">
-        <v>0.011102781390845818</v>
+        <v>0.010558448513836654</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.048670467080817313</v>
       </c>
       <c r="B27">
-        <v>0.010765469929136164</v>
+        <v>0.010235185752817618</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.050542408122387215</v>
       </c>
       <c r="B28">
-        <v>0.010374186277167758</v>
+        <v>0.0098606426586530758</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.052414349163957111</v>
       </c>
       <c r="B29">
-        <v>0.0099275039472385453</v>
+        <v>0.0094334539378799209</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.054286290205527013</v>
       </c>
       <c r="B30">
-        <v>0.0094245461821728729</v>
+        <v>0.0089528127506742772</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.0561582312470969</v>
       </c>
       <c r="B31">
-        <v>0.0088666351469006977</v>
+        <v>0.0084201460717691825</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.0580301722886668</v>
       </c>
       <c r="B32">
-        <v>0.00825564273687837</v>
+        <v>0.0078374393295369011</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.0599021133302367</v>
       </c>
       <c r="B33">
-        <v>0.007593440847562246</v>
+        <v>0.0072066779523497059</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.061774054371806594</v>
       </c>
       <c r="B34">
-        <v>0.0068808824307245763</v>
+        <v>0.0065288418338101646</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.0636459954133765</v>
       </c>
       <c r="B35">
-        <v>0.0061147446634011761</v>
+        <v>0.0058008887284420642</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.065517936454946385</v>
       </c>
       <c r="B36">
-        <v>0.0052907857789437568</v>
+        <v>0.0050187708559994949</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.067389877496516287</v>
       </c>
       <c r="B37">
-        <v>0.0044047640107040186</v>
+        <v>0.0041784404362365394</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.069261818538086176</v>
       </c>
       <c r="B38">
-        <v>0.0034500123925499857</v>
+        <v>0.0032734428501719334</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.071133759579656078</v>
       </c>
       <c r="B39">
-        <v>0.0024101631604149204</v>
+        <v>0.0022876961238829977</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.07300570062122598</v>
       </c>
       <c r="B40">
-        <v>0.001266423350748398</v>
+        <v>0.0012027114447116963</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.07300570062122598</v>
       </c>
       <c r="B43">
-        <v>0.00044485135888236964</v>
+        <v>0.00038113945284566766</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.071133759579656078</v>
       </c>
       <c r="B44">
-        <v>0.00090811766865923785</v>
+        <v>0.00078565063212731516</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.069261818538086176</v>
       </c>
       <c r="B45">
-        <v>0.0013738196520658192</v>
+        <v>0.0011972501096877671</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.067389877496516287</v>
       </c>
       <c r="B46">
-        <v>0.0018259780318373295</v>
+        <v>0.0015996544573698495</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.065517936454946385</v>
       </c>
       <c r="B47">
-        <v>0.0022508920510762652</v>
+        <v>0.0019788771281320037</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.0636459954133765</v>
       </c>
       <c r="B48">
-        <v>0.0026439750343542384</v>
+        <v>0.0023301190993951265</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.061774054371806594</v>
       </c>
       <c r="B49">
-        <v>0.0030029188266101469</v>
+        <v>0.0026508782296957353</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.0599021133302367</v>
       </c>
       <c r="B50">
-        <v>0.0033254152727828813</v>
+        <v>0.0029386523775703412</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.0580301722886668</v>
       </c>
       <c r="B51">
-        <v>0.0036100546097427655</v>
+        <v>0.0031918512024012987</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.0561582312470969</v>
       </c>
       <c r="B52">
-        <v>0.0038590206420858367</v>
+        <v>0.0034125315669543224</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.054286290205527013</v>
       </c>
       <c r="B53">
-        <v>0.0040753955663395619</v>
+        <v>0.0036036621348409657</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.052414349163957111</v>
       </c>
       <c r="B54">
-        <v>0.0042622615790314112</v>
+        <v>0.0037682115696727873</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.050542408122387215</v>
       </c>
       <c r="B55">
-        <v>0.0044220623926255155</v>
+        <v>0.0039085187741108324</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.048670467080817313</v>
       </c>
       <c r="B56">
-        <v>0.0045546877833326713</v>
+        <v>0.0040244036070141249</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.046798526039247418</v>
       </c>
       <c r="B57">
-        <v>0.0046593890433003406</v>
+        <v>0.0041150561662911794</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.044926584997677529</v>
       </c>
       <c r="B58">
-        <v>0.0047354174646759865</v>
+        <v>0.00417966654985051</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.043054643956107627</v>
       </c>
       <c r="B59">
-        <v>0.0047821170464502506</v>
+        <v>0.0042175245116567771</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.041182702914537732</v>
       </c>
       <c r="B60">
-        <v>0.0047992026149864982</v>
+        <v>0.0042283184298992195</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.03931076187296783</v>
       </c>
       <c r="B61">
-        <v>0.0047864817034912778</v>
+        <v>0.0042118363388232213</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.037438820831397934</v>
       </c>
       <c r="B62">
-        <v>0.0047437618451711362</v>
+        <v>0.0041678662726741655</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.035566879789828039</v>
       </c>
       <c r="B63">
-        <v>0.004671609270364265</v>
+        <v>0.0040969616151836389</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.033694938748258144</v>
       </c>
       <c r="B64">
-        <v>0.0045736249979354366</v>
+        <v>0.0040027371480280474</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.031822997706688248</v>
       </c>
       <c r="B65">
-        <v>0.004454168743881071</v>
+        <v>0.0038895730023700012</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.029951056665118349</v>
       </c>
       <c r="B66">
-        <v>0.0043176002241975854</v>
+        <v>0.0037618493093721085</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.028079115623548451</v>
       </c>
       <c r="B67">
-        <v>0.0041624679878496324</v>
+        <v>0.0036181406939330358</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.026207174581978555</v>
       </c>
       <c r="B68">
-        <v>0.00396407591567481</v>
+        <v>0.00343379975589567</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.024335233540408657</v>
       </c>
       <c r="B69">
-        <v>0.003703189001396592</v>
+        <v>0.0031896488466775248</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.022463292498838765</v>
       </c>
       <c r="B70">
-        <v>0.0034056613584090276</v>
+        <v>0.0029116113490504037</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.020591351457268866</v>
       </c>
       <c r="B71">
-        <v>0.0030996763142066477</v>
+        <v>0.0026279475008368336</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.018719410415698967</v>
       </c>
       <c r="B72">
-        <v>0.0027776449330153478</v>
+        <v>0.0023311639287079589</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.016847469374129072</v>
       </c>
       <c r="B73">
-        <v>0.0024271827396456663</v>
+        <v>0.0020089816016802434</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.014975528332559175</v>
       </c>
       <c r="B74">
-        <v>0.0020524953645153516</v>
+        <v>0.0016657324693028113</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.013103587290989278</v>
       </c>
       <c r="B75">
-        <v>0.0016619987365060426</v>
+        <v>0.0013099703189910677</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.011231646249419382</v>
       </c>
       <c r="B76">
-        <v>0.0012643598727477294</v>
+        <v>0.00095052530909286754</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0093597052078494836</v>
       </c>
       <c r="B77">
-        <v>0.0008674785071705796</v>
+        <v>0.00059547504860526319</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0074877641662795874</v>
       </c>
       <c r="B78">
-        <v>0.00047593415265712019</v>
+        <v>0.00024961057818964025</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0056158231247096912</v>
       </c>
       <c r="B79">
-        <v>9.8187974637434954E-05</v>
+        <v>-7.8378729695059341E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0037438820831397937</v>
       </c>
       <c r="B80">
-        <v>-0.00025023944786422837</v>
+        <v>-0.00037270648439613469</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0018719410415698968</v>
       </c>
       <c r="B81">
-        <v>-0.00052955224161106945</v>
+        <v>-0.00059327718452824362</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-3.8647601754498844E-17</v>
+        <v>3.8647601754498844E-17</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.002175666560754054</v>
       </c>
       <c r="B2">
-        <v>0.00095096917923236221</v>
+        <v>0.00092547548204667811</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.004351333121508108</v>
       </c>
       <c r="B3">
-        <v>0.0014855843020156216</v>
+        <v>0.0014359704734397177</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0065269996822621629</v>
       </c>
       <c r="B4">
-        <v>0.0019485173751556176</v>
+        <v>0.0018761462651824292</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0087026662430162161</v>
       </c>
       <c r="B5">
-        <v>0.0023589579727360146</v>
+        <v>0.0022651823674023613</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.01087833280377027</v>
       </c>
       <c r="B6">
-        <v>0.00272474731261389</v>
+        <v>0.0026109105377484258</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.013053999364524326</v>
       </c>
       <c r="B7">
-        <v>0.0030503717409128849</v>
+        <v>0.0029178084314508716</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.01522966592527838</v>
       </c>
       <c r="B8">
-        <v>0.003338479430946215</v>
+        <v>0.003188515912794307</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.017405332486032432</v>
       </c>
       <c r="B9">
-        <v>0.0035931923897742162</v>
+        <v>0.0034271475157234984</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.019580999046786486</v>
       </c>
       <c r="B10">
-        <v>0.0038189577202988418</v>
+        <v>0.0036381432742079818</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.02175666560754054</v>
       </c>
       <c r="B11">
-        <v>0.0040200490750414179</v>
+        <v>0.0038257705526562116</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.023932332168294598</v>
       </c>
       <c r="B12">
-        <v>0.0041987561271101953</v>
+        <v>0.0039923131195476538</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.026107998729048652</v>
       </c>
       <c r="B13">
-        <v>0.0043496060823417435</v>
+        <v>0.0041322930292068934</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.028283665289802702</v>
       </c>
       <c r="B14">
-        <v>0.0044693312487416956</v>
+        <v>0.0042424378265547976</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.03045933185055676</v>
       </c>
       <c r="B15">
-        <v>0.0045712468102636</v>
+        <v>0.0043360587330522485</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.03263499841131081</v>
       </c>
       <c r="B16">
-        <v>0.0046675653674768027</v>
+        <v>0.0044253647226715183</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.034810664972064864</v>
       </c>
       <c r="B17">
-        <v>0.0047495063114659309</v>
+        <v>0.0045015721028904233</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.036986331532818925</v>
       </c>
       <c r="B18">
-        <v>0.0048057264542614043</v>
+        <v>0.0045533350391575925</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.039161998093572972</v>
       </c>
       <c r="B19">
-        <v>0.0048356255011615381</v>
+        <v>0.0045800517952993584</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.041337664654327026</v>
       </c>
       <c r="B20">
-        <v>0.00484128888078162</v>
+        <v>0.0045838066597364826</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.04351333121508108</v>
       </c>
       <c r="B21">
-        <v>0.00482480202173694</v>
+        <v>0.0045666839208897241</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.045688997775835134</v>
       </c>
       <c r="B22">
-        <v>0.0047878785093569323</v>
+        <v>0.0045303963967308946</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.047864664336589195</v>
       </c>
       <c r="B23">
-        <v>0.0047307445558276255</v>
+        <v>0.0044751710234360049</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.050040330897343249</v>
       </c>
       <c r="B24">
-        <v>0.0046532545300491919</v>
+        <v>0.0044008632667321187</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.0522159974580973</v>
       </c>
       <c r="B25">
-        <v>0.0045552628009218081</v>
+        <v>0.0043073285923463005</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.05439166401885135</v>
       </c>
       <c r="B26">
-        <v>0.0044365613286915092</v>
+        <v>0.0041943604189650114</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.056567330579605404</v>
       </c>
       <c r="B27">
-        <v>0.00429669243898777</v>
+        <v>0.004061503977112307</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.058742997140359465</v>
       </c>
       <c r="B28">
-        <v>0.0041351360487859277</v>
+        <v>0.0039082424502716422</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.060918663701113519</v>
       </c>
       <c r="B29">
-        <v>0.0039513720750613207</v>
+        <v>0.0037340590219264703</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.063094330261867573</v>
       </c>
       <c r="B30">
-        <v>0.0037451550035518953</v>
+        <v>0.0035387118169356926</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.06526999682262162</v>
       </c>
       <c r="B31">
-        <v>0.003517337595046049</v>
+        <v>0.0033230587256599989</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.067445663383375681</v>
       </c>
       <c r="B32">
-        <v>0.0032690471790947861</v>
+        <v>0.0030882325798355214</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.069621329944129728</v>
       </c>
       <c r="B33">
-        <v>0.0030014110852491136</v>
+        <v>0.0028353662111983958</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.071796996504883789</v>
       </c>
       <c r="B34">
-        <v>0.0027151092237060886</v>
+        <v>0.0025651454348395992</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.07397266306563785</v>
       </c>
       <c r="B35">
-        <v>0.0024090318272469696</v>
+        <v>0.0022764679992694796</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.0761483296263919</v>
       </c>
       <c r="B36">
-        <v>0.0020816217092990662</v>
+        <v>0.0019677846363532281</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.078323996187145944</v>
       </c>
       <c r="B37">
-        <v>0.0017313216832896851</v>
+        <v>0.0016375460779560317</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.0804996627479</v>
       </c>
       <c r="B38">
-        <v>0.0013554795819088919</v>
+        <v>0.00128310845396087</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.082675329308654052</v>
       </c>
       <c r="B39">
-        <v>0.00094706331489777609</v>
+        <v>0.00089744948632187235</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.084850995869408113</v>
       </c>
       <c r="B40">
-        <v>0.00049794581126018334</v>
+        <v>0.00047245229501095544</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.087026662430162161</v>
       </c>
       <c r="B41">
-        <v>-3.8647601754498844E-17</v>
+        <v>3.8647601754498844E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.087026662430162161</v>
       </c>
       <c r="B42">
-        <v>-3.8647601754498844E-17</v>
+        <v>3.8647601754498844E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.084850995869408113</v>
       </c>
       <c r="B43">
-        <v>0.00011599645062092586</v>
+        <v>9.05029343716979E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.082675329308654052</v>
       </c>
       <c r="B44">
-        <v>0.00024876137555815631</v>
+        <v>0.00019914754698225243</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.0804996627479</v>
       </c>
       <c r="B45">
-        <v>0.00039025620812924166</v>
+        <v>0.0003178850801812198</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.078323996187145944</v>
       </c>
       <c r="B46">
-        <v>0.00053244238165177122</v>
+        <v>0.00043866677631811785</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.0761483296263919</v>
       </c>
       <c r="B47">
-        <v>0.00066837311116572983</v>
+        <v>0.00055453603821989134</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.07397266306563785</v>
       </c>
       <c r="B48">
-        <v>0.00079546873860068248</v>
+        <v>0.00066290491062319249</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.071796996504883789</v>
       </c>
       <c r="B49">
-        <v>0.000912241387608591</v>
+        <v>0.00076227759874210191</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.069621329944129728</v>
       </c>
       <c r="B50">
-        <v>0.001017203181841416</v>
+        <v>0.00085115830779069817</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.067445663383375681</v>
       </c>
       <c r="B51">
-        <v>0.0011093101961888337</v>
+        <v>0.000928495596929569</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.06526999682262162</v>
       </c>
       <c r="B52">
-        <v>0.0011892943104913829</v>
+        <v>0.00099501544110533273</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.063094330261867573</v>
       </c>
       <c r="B53">
-        <v>0.0012583313558273176</v>
+        <v>0.0010518881692111149</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.060918663701113519</v>
       </c>
       <c r="B54">
-        <v>0.001317597163274893</v>
+        <v>0.0011002841101400429</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.058742997140359465</v>
       </c>
       <c r="B55">
-        <v>0.0013679897309288771</v>
+        <v>0.0011410961324145913</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.056567330579605404</v>
       </c>
       <c r="B56">
-        <v>0.0014092957249500924</v>
+        <v>0.0011741072630746302</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.05439166401885135</v>
       </c>
       <c r="B57">
-        <v>0.0014410239785158767</v>
+        <v>0.0011988230687893797</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.0522159974580973</v>
       </c>
       <c r="B58">
-        <v>0.001462683324803566</v>
+        <v>0.0012147491162280586</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.050040330897343249</v>
       </c>
       <c r="B59">
-        <v>0.0014738418081206696</v>
+        <v>0.001221450544803597</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.047864664336589195</v>
       </c>
       <c r="B60">
-        <v>0.0014743043172953843</v>
+        <v>0.0012187307849037639</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.045688997775835134</v>
       </c>
       <c r="B61">
-        <v>0.0014639349522860775</v>
+        <v>0.0012064528396600392</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.04351333121508108</v>
       </c>
       <c r="B62">
-        <v>0.0014425978130511183</v>
+        <v>0.0011844797122039024</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.041337664654327026</v>
       </c>
       <c r="B63">
-        <v>0.0014105255355057074</v>
+        <v>0.0011530433144605696</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.039161998093572972</v>
       </c>
       <c r="B64">
-        <v>0.0013694248993923797</v>
+        <v>0.0011138511935302002</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.036986331532818925</v>
       </c>
       <c r="B65">
-        <v>0.0013213712204105028</v>
+        <v>0.0010689798053066905</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.034810664972064864</v>
       </c>
       <c r="B66">
-        <v>0.0012684398142594441</v>
+        <v>0.0010205056056839367</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.03263499841131081</v>
       </c>
       <c r="B67">
-        <v>0.0012100176067603343</v>
+        <v>0.00096781696195504994</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.03045933185055676</v>
       </c>
       <c r="B68">
-        <v>0.0011347379642213571</v>
+        <v>0.00089954988701000551</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.028283665289802702</v>
       </c>
       <c r="B69">
-        <v>0.0010337929726038193</v>
+        <v>0.00080689955041692073</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.026107998729048652</v>
       </c>
       <c r="B70">
-        <v>0.00091936315599447176</v>
+        <v>0.0007020501028596215</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.023932332168294598</v>
       </c>
       <c r="B71">
-        <v>0.00080472867489188716</v>
+        <v>0.00059828566732934656</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.02175666560754054</v>
       </c>
       <c r="B72">
-        <v>0.00068657979731648658</v>
+        <v>0.00049230127493128033</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.019580999046786486</v>
       </c>
       <c r="B73">
-        <v>0.00055939829878984563</v>
+        <v>0.00037858385269898552</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.017405332486032432</v>
       </c>
       <c r="B74">
-        <v>0.00042542187731631339</v>
+        <v>0.00025937700326559562</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.01522966592527838</v>
       </c>
       <c r="B75">
-        <v>0.0002888688909219752</v>
+        <v>0.00013890537277006643</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.013053999364524326</v>
       </c>
       <c r="B76">
-        <v>0.00015412441523708769</v>
+        <v>2.1561105775074516E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.01087833280377027</v>
       </c>
       <c r="B77">
-        <v>2.5244964803522729E-05</v>
+        <v>-8.85918100619412E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0087026662430162161</v>
       </c>
       <c r="B78">
-        <v>-9.5193907794558053E-05</v>
+        <v>-0.00018896951312821146</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0065269996822621629</v>
       </c>
       <c r="B79">
-        <v>-0.00020278172011799114</v>
+        <v>-0.00027515283009117952</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.004351333121508108</v>
       </c>
       <c r="B80">
-        <v>-0.00028975961155968647</v>
+        <v>-0.00033937344013559043</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.002175666560754054</v>
       </c>
       <c r="B81">
-        <v>-0.00033702542473403784</v>
+        <v>-0.00036251912191972188</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-3.8647601754498844E-17</v>
+        <v>3.8647601754498844E-17</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0</v>
+        <v>8.6456117075814577E-17</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.002433523354040866</v>
       </c>
       <c r="B2">
-        <v>0.00070708325782222045</v>
+        <v>0.00069432010578177462</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.004867046708081732</v>
       </c>
       <c r="B3">
-        <v>0.0010697471775706871</v>
+        <v>0.001044883285525757</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.007300570062122598</v>
       </c>
       <c r="B4">
-        <v>0.0013771002243370555</v>
+        <v>0.0013407967508180616</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.009734093416163464</v>
       </c>
       <c r="B5">
-        <v>0.0016452092182854337</v>
+        <v>0.0015981261381082645</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.012167616770204328</v>
       </c>
       <c r="B6">
-        <v>0.0018806227865347275</v>
+        <v>0.0018234189563162426</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.014601140124245196</v>
       </c>
       <c r="B7">
-        <v>0.0020870775191954233</v>
+        <v>0.0020204107622125173</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.017034663478286062</v>
       </c>
       <c r="B8">
-        <v>0.002266769144219534</v>
+        <v>0.0021912962931156486</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.019468186832326928</v>
       </c>
       <c r="B9">
-        <v>0.0024231323206608149</v>
+        <v>0.00233950931180009</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.021901710186367791</v>
       </c>
       <c r="B10">
-        <v>0.0025598756639535749</v>
+        <v>0.0024687575835964</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.024335233540408657</v>
       </c>
       <c r="B11">
-        <v>0.002680564683952598</v>
+        <v>0.0025826058586036703</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.026768756894449526</v>
       </c>
       <c r="B12">
-        <v>0.0027871017342856194</v>
+        <v>0.0026829557754465211</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.029202280248490392</v>
       </c>
       <c r="B13">
-        <v>0.0028748796492517026</v>
+        <v>0.0027651995420831595</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.031635803602531258</v>
       </c>
       <c r="B14">
-        <v>0.0029411423035730151</v>
+        <v>0.0028265804530665118</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.034069326956572124</v>
       </c>
       <c r="B15">
-        <v>0.0029970472529928173</v>
+        <v>0.0028782555799947897</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.036502850310612983</v>
       </c>
       <c r="B16">
-        <v>0.0030528281540518226</v>
+        <v>0.0029304581356450581</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.038936373664653856</v>
       </c>
       <c r="B17">
-        <v>0.0031011093854594681</v>
+        <v>0.0029758121204645051</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.041369897018694722</v>
       </c>
       <c r="B18">
-        <v>0.0031323669740054073</v>
+        <v>0.0030047932362761783</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.043803420372735581</v>
       </c>
       <c r="B19">
-        <v>0.0031460928166314344</v>
+        <v>0.003016893202736438</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.046236943726776454</v>
       </c>
       <c r="B20">
-        <v>0.00314403277781738</v>
+        <v>0.003013857743959973</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.048670467080817313</v>
       </c>
       <c r="B21">
-        <v>0.0031279327220430754</v>
+        <v>0.0029974325840614728</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.051103990434858179</v>
       </c>
       <c r="B22">
-        <v>0.0030992277488310527</v>
+        <v>0.0029690527281108926</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.053537513788899052</v>
       </c>
       <c r="B23">
-        <v>0.0030581098978746521</v>
+        <v>0.0029289103049992514</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.055971037142939918</v>
       </c>
       <c r="B24">
-        <v>0.0030044604439099175</v>
+        <v>0.0028768867245728348</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.058404560496980784</v>
       </c>
       <c r="B25">
-        <v>0.0029381606616728914</v>
+        <v>0.0028128633966779284</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.060838083851021643</v>
       </c>
       <c r="B26">
-        <v>0.0028590406043134645</v>
+        <v>0.0027366705537967763</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.063271607205062516</v>
       </c>
       <c r="B27">
-        <v>0.0027667254386369161</v>
+        <v>0.0026479337189554528</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.065705130559103375</v>
       </c>
       <c r="B28">
-        <v>0.0026607891098623759</v>
+        <v>0.0025462272378159925</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.068138653913144248</v>
       </c>
       <c r="B29">
-        <v>0.0025408055632089714</v>
+        <v>0.0024311254560404291</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.070572177267185107</v>
       </c>
       <c r="B30">
-        <v>0.0024065802353684441</v>
+        <v>0.0023024342554120139</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.073005700621225966</v>
       </c>
       <c r="B31">
-        <v>0.0022588445289229843</v>
+        <v>0.0021608856621988704</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.075439223975266839</v>
       </c>
       <c r="B32">
-        <v>0.0020985613379273949</v>
+        <v>0.0020074432387903363</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.077872747329307712</v>
       </c>
       <c r="B33">
-        <v>0.0019266935564364782</v>
+        <v>0.0018430705475757534</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.080306270683348571</v>
       </c>
       <c r="B34">
-        <v>0.0017438299800486251</v>
+        <v>0.0016683570989567151</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.082739794037389444</v>
       </c>
       <c r="B35">
-        <v>0.0015490630105365708</v>
+        <v>0.0014823961953838311</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.0851733173914303</v>
       </c>
       <c r="B36">
-        <v>0.0013411109512166395</v>
+        <v>0.0012839070873199663</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.087606840745471162</v>
       </c>
       <c r="B37">
-        <v>0.0011186921054051524</v>
+        <v>0.001071609025227983</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.090040364099512035</v>
       </c>
       <c r="B38">
-        <v>0.00087960735573764976</v>
+        <v>0.000843303880729557</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.092473887453552908</v>
       </c>
       <c r="B39">
-        <v>0.00061798790212654</v>
+        <v>0.0005931240100816098</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.094907410807593767</v>
       </c>
       <c r="B40">
-        <v>0.00032704752380344784</v>
+        <v>0.00031428439069987481</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.097340934161634626</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>8.6456117075814577E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.097340934161634626</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>8.6453478644507327E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.094907410807593767</v>
       </c>
       <c r="B43">
-        <v>6.6344469756968169E-06</v>
+        <v>-6.1286861278761764E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.092473887453552908</v>
       </c>
       <c r="B44">
-        <v>3.2190160341823872E-05</v>
+        <v>7.3262682968937822E-06</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.090040364099512035</v>
       </c>
       <c r="B45">
-        <v>6.9892186948824816E-05</v>
+        <v>3.3588711940732E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.087606840745471162</v>
       </c>
       <c r="B46">
-        <v>0.00011296557364714332</v>
+        <v>6.5882493469974007E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.0851733173914303</v>
       </c>
       <c r="B47">
-        <v>0.00015555239734831771</v>
+        <v>9.8348533451644621E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.082739794037389444</v>
       </c>
       <c r="B48">
-        <v>0.00019546285520826494</v>
+        <v>0.00012879604005552528</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.080306270683348571</v>
       </c>
       <c r="B49">
-        <v>0.00023142417444399716</v>
+        <v>0.00015595129335208721</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.077872747329307712</v>
       </c>
       <c r="B50">
-        <v>0.000262163582272526</v>
+        <v>0.00017854057341180101</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.075439223975266839</v>
       </c>
       <c r="B51">
-        <v>0.00028678196834450924</v>
+        <v>0.00019566386920745094</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.073005700621225966</v>
       </c>
       <c r="B52">
-        <v>0.00030587487204518897</v>
+        <v>0.00020791600532107463</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.070572177267185107</v>
       </c>
       <c r="B53">
-        <v>0.00032041149519345308</v>
+        <v>0.00021626551523702296</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.068138653913144248</v>
       </c>
       <c r="B54">
-        <v>0.00033136103960818952</v>
+        <v>0.00022168093243964704</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.065705130559103375</v>
       </c>
       <c r="B55">
-        <v>0.00033946079489090172</v>
+        <v>0.00022489892284451835</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.063271607205062516</v>
       </c>
       <c r="B56">
-        <v>0.00034452040177355482</v>
+        <v>0.0002257286820920914</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.060838083851021643</v>
       </c>
       <c r="B57">
-        <v>0.00034611758877072939</v>
+        <v>0.00022374753825404124</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.058404560496980784</v>
       </c>
       <c r="B58">
-        <v>0.000343830084397006</v>
+        <v>0.00021853281940204303</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.055971037142939918</v>
       </c>
       <c r="B59">
-        <v>0.00033728642106719962</v>
+        <v>0.00020971270173011667</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.053537513788899052</v>
       </c>
       <c r="B60">
-        <v>0.00032631834679706326</v>
+        <v>0.00019711875392166206</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.051103990434858179</v>
       </c>
       <c r="B61">
-        <v>0.00031080841350258421</v>
+        <v>0.00018063339278242397</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.048670467080817313</v>
       </c>
       <c r="B62">
-        <v>0.00029063917309974979</v>
+        <v>0.00016013903511814709</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.046236943726776454</v>
       </c>
       <c r="B63">
-        <v>0.00026600350847151355</v>
+        <v>0.00013582847461410626</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.043803420372735581</v>
       </c>
       <c r="B64">
-        <v>0.00023833562636869251</v>
+        <v>0.00010913601247369609</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.041369897018694722</v>
       </c>
       <c r="B65">
-        <v>0.00020938006450907013</v>
+        <v>8.1806326779841355E-05</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.038936373664653856</v>
       </c>
       <c r="B66">
-        <v>0.00018088136061042957</v>
+        <v>5.5584095615466609E-05</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.036502850310612983</v>
       </c>
       <c r="B67">
-        <v>0.00015232973605238146</v>
+        <v>2.9959717645616888E-05</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.034069326956572124</v>
       </c>
       <c r="B68">
-        <v>0.00011419814686184599</v>
+        <v>-4.5935261361816336E-06</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.031635803602531258</v>
       </c>
       <c r="B69">
-        <v>5.9107397755965068E-05</v>
+        <v>-5.5454452750538091E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.029202280248490392</v>
       </c>
       <c r="B70">
-        <v>-2.7130464345402797E-06</v>
+        <v>-0.00011239315360308282</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.026768756894449526</v>
       </c>
       <c r="B71">
-        <v>-6.0110202351789647E-05</v>
+        <v>-0.00016425616119088786</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.024335233540408657</v>
       </c>
       <c r="B72">
-        <v>-0.00011584567264284136</v>
+        <v>-0.00021380449799176897</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.021901710186367791</v>
       </c>
       <c r="B73">
-        <v>-0.00017453253508252438</v>
+        <v>-0.00026565061543969913</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.019468186832326928</v>
       </c>
       <c r="B74">
-        <v>-0.00023427518195181065</v>
+        <v>-0.00031789819081253564</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.017034663478286062</v>
       </c>
       <c r="B75">
-        <v>-0.0002915152697669269</v>
+        <v>-0.00036698812087081212</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.014601140124245196</v>
       </c>
       <c r="B76">
-        <v>-0.00034255219747897711</v>
+        <v>-0.00040921895446188294</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.012167616770204328</v>
       </c>
       <c r="B77">
-        <v>-0.00038395975319778015</v>
+        <v>-0.00044116358341626523</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.009734093416163464</v>
       </c>
       <c r="B78">
-        <v>-0.00041355153923313819</v>
+        <v>-0.00046063461941030746</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.007300570062122598</v>
       </c>
       <c r="B79">
-        <v>-0.00042760069501965038</v>
+        <v>-0.00046390416853864426</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.004867046708081732</v>
       </c>
       <c r="B80">
-        <v>-0.0004195691151023221</v>
+        <v>-0.00044443300714725224</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.002433523354040866</v>
       </c>
       <c r="B81">
-        <v>-0.00037340111137192371</v>
+        <v>-0.00038616426341236954</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>8.6456117075814577E-17</v>
       </c>
     </row>
   </sheetData>
